--- a/docs/_baseline/bird_report.xlsx
+++ b/docs/_baseline/bird_report.xlsx
@@ -1,14 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <bookViews>
-    <workbookView activeTab="3"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="조사개황" state="visible" r:id="rId1"/>
     <sheet sheetId="2" name="출현종" state="visible" r:id="rId2"/>
     <sheet sheetId="3" name="출현종요약" state="visible" r:id="rId3"/>
-    <sheet sheetId="4" name="License" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">출현종!$A$3:$R$7</definedName>
@@ -18,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87">
   <si>
     <t>조류 조사결과 — 조사개황</t>
   </si>
@@ -146,7 +142,7 @@
     <t>매과</t>
   </si>
   <si>
-    <t>국명</t>
+    <t>일반명</t>
   </si>
   <si>
     <t>붉은머리오목눈이</t>
@@ -279,9 +275,6 @@
   </si>
   <si>
     <t>기타 도래유형 개체수</t>
-  </si>
-  <si>
-    <t>Thank you for using version 2026.2.519.80 of Telerik Document Processing Libraries. License validation couldn't run, possibly due to a missing Telerik.Licensing NuGet package reference to BaselineGen. See documentation for setup. Learn more about Telerik Document Processing Libraries licensing https://docs.telerik.com/devtools/document-processing/distribution-and-licensing/license-key</t>
   </si>
 </sst>
 </file>
@@ -289,7 +282,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <b val="false"/>
       <i val="false"/>
@@ -347,15 +340,6 @@
       <color rgb="FF0381FE"/>
       <name val="맑은 고딕"/>
     </font>
-    <font>
-      <b val="false"/>
-      <i val="false"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -388,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
     <xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" borderId="0" xfId="0" applyFont="true"/>
@@ -402,7 +386,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="7" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="28.57421875" hidden="false" outlineLevel="0"/>
@@ -678,6 +661,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
@@ -1266,19 +1253,4 @@
   <autoFilter ref="A3:R4"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
-</worksheet>
 </file>
--- a/docs/_baseline/bird_report.xlsx
+++ b/docs/_baseline/bird_report.xlsx
@@ -7,14 +7,14 @@
     <sheet sheetId="3" name="출현종요약" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">출현종!$A$3:$R$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">출현종요약!$A$3:$R$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">출현종!$A$3:$R$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">출현종요약!$A$3:$Q$4</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96">
   <si>
     <t>조류 조사결과 — 조사개황</t>
   </si>
@@ -127,6 +127,9 @@
     <t>매목</t>
   </si>
   <si>
+    <t>파랑새목</t>
+  </si>
+  <si>
     <t>과</t>
   </si>
   <si>
@@ -142,6 +145,12 @@
     <t>매과</t>
   </si>
   <si>
+    <t>까마귀과</t>
+  </si>
+  <si>
+    <t>물총새과</t>
+  </si>
+  <si>
     <t>일반명</t>
   </si>
   <si>
@@ -157,6 +166,12 @@
     <t>황조롱이</t>
   </si>
   <si>
+    <t>까치</t>
+  </si>
+  <si>
+    <t>물총새</t>
+  </si>
+  <si>
     <t>학명</t>
   </si>
   <si>
@@ -172,13 +187,22 @@
     <t>Falco tinnunculus</t>
   </si>
   <si>
+    <t>Pica serica</t>
+  </si>
+  <si>
+    <t>Alcedo atthis</t>
+  </si>
+  <si>
     <t>개체수</t>
   </si>
   <si>
     <t>도래유형</t>
   </si>
   <si>
-    <t>텃새</t>
+    <t>RES</t>
+  </si>
+  <si>
+    <t>SV</t>
   </si>
   <si>
     <t>대항목</t>
@@ -211,6 +235,12 @@
     <t>비행</t>
   </si>
   <si>
+    <t>교목</t>
+  </si>
+  <si>
+    <t>횃대</t>
+  </si>
+  <si>
     <t>서식유형</t>
   </si>
   <si>
@@ -259,19 +289,16 @@
     <t>생태계교란생물</t>
   </si>
   <si>
-    <t>텃새 개체수</t>
-  </si>
-  <si>
-    <t>여름철새 개체수</t>
-  </si>
-  <si>
-    <t>겨울철새 개체수</t>
-  </si>
-  <si>
-    <t>나그네새 개체수</t>
-  </si>
-  <si>
-    <t>길잃은새 개체수</t>
+    <t>RES · 텃새 개체수</t>
+  </si>
+  <si>
+    <t>SV · 여름철새 개체수</t>
+  </si>
+  <si>
+    <t>WV · 겨울철새 개체수</t>
+  </si>
+  <si>
+    <t>PM · 통과철새 개체수</t>
   </si>
   <si>
     <t>기타 도래유형 개체수</t>
@@ -673,7 +700,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="12.8515625" hidden="false" outlineLevel="0"/>
@@ -751,28 +778,28 @@
         <v>32</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>12</v>
@@ -781,13 +808,13 @@
         <v>13</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -807,28 +834,28 @@
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="N4" s="7" t="n">
         <v>36.763081</v>
@@ -837,10 +864,10 @@
         <v>127.090606</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="R4" s="2"/>
     </row>
@@ -861,28 +888,28 @@
         <v>34</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>18</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>36.763081</v>
@@ -891,10 +918,10 @@
         <v>127.090606</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="R5" s="2"/>
     </row>
@@ -915,28 +942,28 @@
         <v>35</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>36.763081</v>
@@ -945,10 +972,10 @@
         <v>127.090606</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="R6" s="2"/>
     </row>
@@ -969,28 +996,28 @@
         <v>36</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="N7" s="7" t="n">
         <v>36.763081</v>
@@ -999,24 +1026,130 @@
         <v>127.090606</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>71</v>
-      </c>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>36.763081</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>127.090606</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>36.763081</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>127.090606</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="R9" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R7"/>
+  <autoFilter ref="A3:R9"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="12.8515625" hidden="false" outlineLevel="0"/>
@@ -1030,12 +1163,12 @@
     <col min="10" max="10" bestFit="false" customWidth="true" width="14.28125" hidden="false" outlineLevel="0"/>
     <col min="11" max="11" bestFit="false" customWidth="true" width="45.7109375" hidden="false" outlineLevel="0"/>
     <col min="12" max="12" bestFit="false" customWidth="true" width="31.421875" hidden="false" outlineLevel="0"/>
-    <col min="13" max="18" bestFit="false" customWidth="true" width="15.7109375" hidden="false" outlineLevel="0"/>
+    <col min="13" max="17" bestFit="false" customWidth="true" width="15.7109375" hidden="false" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1053,7 +1186,6 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
@@ -1073,7 +1205,6 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
@@ -1095,40 +1226,37 @@
         <v>8</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -1154,7 +1282,7 @@
         <v>46156</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>64</v>
@@ -1163,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="7" t="n">
@@ -1179,9 +1307,6 @@
         <v>0</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1203,11 +1328,10 @@
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1225,11 +1349,10 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1247,10 +1370,9 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R4"/>
+  <autoFilter ref="A3:Q4"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
 </file>
--- a/docs/_baseline/bird_report.xlsx
+++ b/docs/_baseline/bird_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94">
   <si>
     <t>조류 조사결과 — 조사개황</t>
   </si>
@@ -43,9 +43,6 @@
     <t>하천명</t>
   </si>
   <si>
-    <t>하천유형</t>
-  </si>
-  <si>
     <t>사업장</t>
   </si>
   <si>
@@ -67,7 +64,7 @@
     <t>조사자</t>
   </si>
   <si>
-    <t>※ 관리자 테이블에 대권역·중권역·하천유형·조사기관 컬럼이 없어 일괄입력 시에는 해당 열이 비워진다.</t>
+    <t>※ 관리자 테이블에 대권역·중권역·조사기관 컬럼이 없어 일괄입력 시에는 해당 열이 비워진다.</t>
   </si>
   <si>
     <t>방류하천</t>
@@ -83,9 +80,6 @@
   </si>
   <si>
     <t>곡교천</t>
-  </si>
-  <si>
-    <t>평지형</t>
   </si>
   <si>
     <t>온양</t>
@@ -532,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="28.57421875" hidden="false" outlineLevel="0"/>
@@ -564,7 +558,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -580,7 +574,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +590,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -604,7 +598,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -612,7 +606,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -620,7 +614,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -628,15 +622,15 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
+      <c r="B14" s="2" t="n">
+        <v>36.763081</v>
       </c>
     </row>
     <row r="15">
@@ -644,15 +638,15 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>36.763081</v>
+        <v>127.090606</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>127.090606</v>
+      <c r="B16" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -660,7 +654,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -668,30 +662,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2"/>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
@@ -721,7 +707,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -763,99 +749,99 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="O3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="Q3" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="R3" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N4" s="7" t="n">
         <v>36.763081</v>
@@ -864,52 +850,52 @@
         <v>127.090606</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>18</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>36.763081</v>
@@ -918,52 +904,52 @@
         <v>127.090606</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>36.763081</v>
@@ -972,52 +958,52 @@
         <v>127.090606</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N7" s="7" t="n">
         <v>36.763081</v>
@@ -1026,54 +1012,54 @@
         <v>127.090606</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>36.763081</v>
@@ -1082,50 +1068,50 @@
         <v>127.090606</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>36.763081</v>
@@ -1134,10 +1120,10 @@
         <v>127.090606</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R9" s="2"/>
     </row>
@@ -1168,7 +1154,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1208,16 +1194,16 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>4</v>
@@ -1226,57 +1212,57 @@
         <v>8</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>46156</v>
@@ -1291,7 +1277,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="7" t="n">
@@ -1331,7 +1317,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1352,7 +1338,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
